--- a/fix-errors/ig/FRSectionConclusionLMCDAFHIR.xlsx
+++ b/fix-errors/ig/FRSectionConclusionLMCDAFHIR.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T08:13:43+00:00</t>
+    <t>2026-08-18T11:25:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -101,13 +101,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-conclusion</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-conclusion|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-dicom-conclusion</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-dicom-conclusion|0.1.0</t>
   </si>
   <si>
     <t>FRLMConclusion</t>
@@ -137,7 +137,7 @@
     <t>FRCDADICOMConclusion.title</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-diagnostic-report-imaging-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-diagnostic-report-imaging-document|0.1.0</t>
   </si>
   <si>
     <t>FRDiagnosticReportImagingDocument.conclusion</t>
@@ -149,7 +149,7 @@
     <t>FRDiagnosticReportImagingDocument.result</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-composition-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-composition-document|0.1.0</t>
   </si>
   <si>
     <t>FRCompositionDocument.section:sectionImpression</t>
